--- a/frontend/e2e/fixtures/ordine758.xlsx
+++ b/frontend/e2e/fixtures/ordine758.xlsx
@@ -427,6 +427,9 @@
           <t>versato</t>
         </is>
       </c>
+      <c r="B1" t="n">
+        <v>397500</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
